--- a/Project Code.xlsx
+++ b/Project Code.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="3" r:id="rId1"/>
@@ -591,7 +591,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,19 +603,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1131,19 +1118,28 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1152,130 +1148,121 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1300,17 +1287,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1325,7 +1312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">

--- a/Project Code.xlsx
+++ b/Project Code.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="3" r:id="rId1"/>
@@ -353,10 +353,10 @@
     <t>Expirements/SceneSegmentation/trial4.ipynb</t>
   </si>
   <si>
-    <t>visual/hog/datastructures/*</t>
-  </si>
-  <si>
-    <t>Implement the structure of needed components and classes</t>
+    <t>visual/hog/datastructures/*.py</t>
+  </si>
+  <si>
+    <t>Implement the structure of needed components and classes for the model</t>
   </si>
   <si>
     <t>visual/hog/features/hog_descriptor.py</t>
@@ -365,28 +365,28 @@
     <t>Implements the HOG feature extractor used for object detection</t>
   </si>
   <si>
-    <t>visual/hog/inference/*</t>
-  </si>
-  <si>
-    <t>Implement functions for inference stage</t>
-  </si>
-  <si>
-    <t>visual/hog/training/*</t>
-  </si>
-  <si>
-    <t>Implement functions for training stage</t>
+    <t>visual/hog/inference/*.py</t>
+  </si>
+  <si>
+    <t>Implement functions for detection/inference and contextual rescoring stages</t>
+  </si>
+  <si>
+    <t>visual/hog/training/*.py</t>
+  </si>
+  <si>
+    <t>Implement functions of main steps for training stage</t>
   </si>
   <si>
     <t>visual/hog/checkpoint.py</t>
   </si>
   <si>
-    <t>Implement checkpointing for divide training on time</t>
+    <t>Implement checkpointing to handle saving and loading the training state so training can be resumed</t>
   </si>
   <si>
     <t>visual/hog/hog_detector.py</t>
   </si>
   <si>
-    <t>Implement the detector class that runs training and inference</t>
+    <t>Implement the detector class (top-level) that runs training and inference</t>
   </si>
   <si>
     <t>visual/hog/ObjectDetector.py</t>
@@ -428,13 +428,13 @@
     <t>Implement an interface to start the training and evaluation</t>
   </si>
   <si>
-    <t>visual/faster_rcnn/model/*</t>
+    <t>visual/faster_rcnn/model/*.py</t>
   </si>
   <si>
     <t>Implement the used networks and model architecture</t>
   </si>
   <si>
-    <t>visual/faster_rcnn/train/*</t>
+    <t>visual/faster_rcnn/train/*.py</t>
   </si>
   <si>
     <t>Implement the training functions and steps</t>
@@ -443,7 +443,7 @@
     <t>Except visualization in visual/faster_rcnn/train/pipeline.py</t>
   </si>
   <si>
-    <t>visual/faster_rcnn/util/*</t>
+    <t>visual/faster_rcnn/util/*.py</t>
   </si>
   <si>
     <t>Implement utily functions that are applied on windows/boxes and evalation function</t>
@@ -464,13 +464,13 @@
     <t>Implements the dataset class responsible for loading the training and evaluation data</t>
   </si>
   <si>
-    <t>visual/vrd_ml/features/*</t>
+    <t>visual/vrd_ml/features/*.py</t>
   </si>
   <si>
     <t>Implement the feature extractor used for predicate detection</t>
   </si>
   <si>
-    <t>visual/vrd_ml/models/*</t>
+    <t>visual/vrd_ml/models/*.py</t>
   </si>
   <si>
     <t>Implment the visual relationship detection pipeline to get ranked relationship triplets</t>
@@ -500,7 +500,7 @@
     <t>visual/vrd_ml/vrd_pipeline.ipynb</t>
   </si>
   <si>
-    <t>Load dataset and running model training and evaluation</t>
+    <t>Load dataset and running model training and evaluation (end-to-end notebook)</t>
   </si>
   <si>
     <t>visual/vrd_ml/VRD.py</t>
@@ -581,7 +581,7 @@
     <t>vidseek-ui/**/*</t>
   </si>
   <si>
-    <t>Storage/SQL/Models/*</t>
+    <t>Storage/SQL/Models/*.py</t>
   </si>
   <si>
     <t>Database schema and ORM models</t>
@@ -1330,7 +1330,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1346,9 +1346,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1800,70 +1797,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="14"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:4">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" ht="125.55" customHeight="1" spans="1:4">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" ht="86.55" customHeight="1" spans="1:4">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" ht="41.55" customHeight="1" spans="1:4">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" ht="62.55" customHeight="1" spans="1:4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1871,10 +1868,10 @@
       <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1885,10 +1882,10 @@
       <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1899,7 +1896,7 @@
       <c r="B12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1910,21 +1907,21 @@
       <c r="A13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1" spans="1:4">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1935,7 +1932,7 @@
       <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1957,7 +1954,7 @@
       <c r="B17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1965,20 +1962,20 @@
       <c r="A18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="4"/>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4"/>
-      <c r="C20" s="10"/>
+      <c r="C20" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2080,13 +2077,13 @@
       <c r="A5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2094,13 +2091,13 @@
       <c r="A6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2122,13 +2119,13 @@
       <c r="A8" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2136,13 +2133,13 @@
       <c r="A9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2150,13 +2147,13 @@
       <c r="A10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2164,13 +2161,13 @@
       <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2178,13 +2175,13 @@
       <c r="A12" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2192,13 +2189,13 @@
       <c r="A13" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2206,181 +2203,181 @@
       <c r="A14" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="11" t="s">
+      <c r="C15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="C16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="11" t="s">
+      <c r="C17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="11" t="s">
+      <c r="C18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="11" t="s">
+      <c r="C19" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="11" t="s">
+      <c r="C20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="11" t="s">
+      <c r="C21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="11" t="s">
+      <c r="C22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:5">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="10" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="11" t="s">
+      <c r="C25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>19</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="10" t="s">
         <v>91</v>
       </c>
       <c r="E26" t="s">
@@ -2388,439 +2385,439 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="11" t="s">
+      <c r="C27" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="11" t="s">
+      <c r="C28" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="11" t="s">
+      <c r="C29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="C30" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="C31" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="E31" s="12"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="12"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="12"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E34" s="12"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="12" t="s">
+      <c r="C35" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="12"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36" s="12" t="s">
+      <c r="C36" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="E36" s="12"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37" s="12" t="s">
+      <c r="C37" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="E37" s="12"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38" s="12" t="s">
+      <c r="C38" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="12"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="12" t="s">
+      <c r="C39" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E39" s="12"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="12" t="s">
+      <c r="C40" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="12"/>
+      <c r="E40" s="11"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E41" s="12"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E42" s="12"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="12" t="s">
+      <c r="C43" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="E43" s="12"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="12" t="s">
+      <c r="C44" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="11" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="12" t="s">
+      <c r="C45" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E45" s="12"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="12" t="s">
+      <c r="C46" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="12" t="s">
+      <c r="C47" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="12" t="s">
+      <c r="C48" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="12" t="s">
+      <c r="C49" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="12" t="s">
+      <c r="C50" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="12" t="s">
+      <c r="C51" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="12" t="s">
+      <c r="C52" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="11" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="12" t="s">
+      <c r="C54" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" s="12" t="s">
+      <c r="C55" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="12" t="s">
+      <c r="C56" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2828,7 +2825,7 @@
       <c r="A57" t="s">
         <v>150</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -2982,13 +2979,13 @@
       <c r="A68" t="s">
         <v>173</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2996,7 +2993,7 @@
       <c r="A69" t="s">
         <v>174</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -3010,7 +3007,7 @@
       <c r="A70" t="s">
         <v>176</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C70" s="1" t="s">
@@ -3025,7 +3022,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B57 B68:B70 B81:B101 B105:B1002">
       <formula1>INDIRECT("Modules[Module Name]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Source" prompt="Please select source..." sqref="C2:C57 C61:C62 C66:C67 C68:C70 C81:C101 C105:C1002">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Source" prompt="Please select source..." sqref="C2:C57 C61:C62 C66:C70 C81:C101 C105:C1002">
       <formula1>'Option Tables'!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -3033,7 +3030,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="E67:E80 A81:E101 E102:E104 E61:E66 A1:E1" listDataValidation="1"/>
+    <ignoredError sqref="A1:E1 E102:E104 A81:E101 E61:E80" listDataValidation="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
